--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_vol/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_vol/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.09771737318994544</v>
+        <v>0.1890338446084483</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2712314465536297</v>
+        <v>0.1683330851134497</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.4686416936320495</v>
+        <v>1.158060168606349</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.6847113165500718</v>
+        <v>1.736410327415427</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.1831847418184631</v>
+        <v>0.1116381348776221</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.6065331205675847</v>
+        <v>1.935807470308795</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>62.46283976136644</v>
+        <v>35.99355760263744</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.255239583632986</v>
+        <v>0.3066783428254836</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2428680631969934</v>
+        <v>0.2863479061283739</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.20290885674031</v>
+        <v>1.063391328088143</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.598505588070666</v>
+        <v>1.65980321697346</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3008272068584671</v>
+        <v>0.1392399077718411</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8784239428217455</v>
+        <v>2.306820562360819</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>62.81572877963619</v>
+        <v>42.53412965738077</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.03612204556609266</v>
+        <v>0.1773103578164807</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2043780626365644</v>
+        <v>0.2374972883013752</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.1586995497505348</v>
+        <v>0.7715834714136486</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.2328740082448236</v>
+        <v>1.130424194782303</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2265789652644169</v>
+        <v>0.1723104996135125</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.1658860495255337</v>
+        <v>1.07525849085142</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>67.0046290819796</v>
+        <v>68.54468092573252</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1095099959918978</v>
+        <v>0.4259587805941814</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2365364225472713</v>
+        <v>0.3379749509065155</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.4564534343128627</v>
+        <v>1.217205844327105</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.6758210415729267</v>
+        <v>1.916537585704411</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2237332928214508</v>
+        <v>0.1478317105676724</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.5084966895340011</v>
+        <v>3.023854940098737</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>75.25760143340086</v>
+        <v>78.58075589296816</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3034078106813536</v>
+        <v>0.3009711551203602</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2158410657145573</v>
+        <v>0.2528761074133432</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.312362925243835</v>
+        <v>1.147559982118413</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.931413726187162</v>
+        <v>1.636249078037042</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1266294263015335</v>
+        <v>0.1952422871671214</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.49754456529073</v>
+        <v>1.60677742944609</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>70.43688023615013</v>
+        <v>84.03464157769227</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.5874480632026435</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3742616730842058</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2.387505522691352</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>3.871151889427729</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1194546865643817</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>10.97746506285174</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>63.17371912125241</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>